--- a/data/availability/projects/mountain-view/mountain-view-grand-valley.xlsx
+++ b/data/availability/projects/mountain-view/mountain-view-grand-valley.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for mountain-view-grand-valley</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -637,7 +647,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>OFF PLAN - 2</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -759,7 +769,6 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -816,7 +825,6 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -873,7 +881,6 @@
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -930,7 +937,6 @@
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -941,7 +947,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>OFF PLAN - 2</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -987,7 +993,6 @@
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -998,7 +1003,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>OFF PLAN - 2</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1044,7 +1049,6 @@
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1055,7 +1059,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>OFF PLAN - 2</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1101,7 +1105,6 @@
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1112,7 +1115,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>OFF PLAN - 2</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1158,7 +1161,6 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1169,7 +1171,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>OFF PLAN - 2</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1215,7 +1217,6 @@
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1226,7 +1227,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>OFF PLAN - 2</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1272,7 +1273,6 @@
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>OFF PLAN - 2</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1329,7 +1329,6 @@
       <c r="G12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1340,7 +1339,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>OFF PLAN - 2</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1386,7 +1385,6 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1397,7 +1395,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>OFF PLAN - 2</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1443,7 +1441,6 @@
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1454,7 +1451,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>OFF PLAN - 2</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1500,7 +1497,6 @@
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1511,7 +1507,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>OFF PLAN - 2</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1557,7 +1553,6 @@
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1568,7 +1563,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>OFF PLAN - 2</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1614,7 +1609,6 @@
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1625,7 +1619,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>OFF PLAN - 2</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1671,7 +1665,6 @@
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1682,7 +1675,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>OFF PLAN - 2</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1728,7 +1721,6 @@
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1785,7 +1777,6 @@
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1842,7 +1833,6 @@
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1899,7 +1889,6 @@
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1956,7 +1945,6 @@
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2013,7 +2001,6 @@
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2070,7 +2057,6 @@
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2127,7 +2113,6 @@
       <c r="G26" t="n">
         <v>0</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2184,7 +2169,6 @@
       <c r="G27" t="n">
         <v>0</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2241,7 +2225,6 @@
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2298,7 +2281,6 @@
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2355,7 +2337,6 @@
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2412,7 +2393,6 @@
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2469,7 +2449,6 @@
       <c r="G32" t="n">
         <v>0</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2526,7 +2505,6 @@
       <c r="G33" t="n">
         <v>0</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2583,7 +2561,6 @@
       <c r="G34" t="n">
         <v>0</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Landscape</t>

--- a/data/availability/projects/mountain-view/mountain-view-grand-valley.xlsx
+++ b/data/availability/projects/mountain-view/mountain-view-grand-valley.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -745,7 +745,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Grand View Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
